--- a/Priyas Expense Summary.xlsx
+++ b/Priyas Expense Summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/659766f1ee369f10/Documents/Anudip Course/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="717" documentId="13_ncr:1_{7E7164A1-2815-4D9C-AF3F-1E975D5B4E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB9C7AC9-30B6-4CBB-B2C2-4FE9BC80E403}"/>
+  <xr:revisionPtr revIDLastSave="773" documentId="13_ncr:1_{7E7164A1-2815-4D9C-AF3F-1E975D5B4E63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A74B1BDD-078A-4615-8BFB-85E511873A56}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Expense" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="57">
   <si>
     <t>Date</t>
   </si>
@@ -410,7 +410,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -508,6 +508,19 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3356,7 +3369,7 @@
       <c r="B1" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="42" t="s">
         <v>14</v>
       </c>
       <c r="D1" s="12" t="s">
@@ -3377,7 +3390,7 @@
         <f>TEXT(A2,"mmmm")</f>
         <v>October</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="13">
@@ -3398,7 +3411,7 @@
         <f t="shared" ref="B3:B51" si="0">TEXT(A3,"mmmm")</f>
         <v>October</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="43" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="13">
@@ -3419,7 +3432,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D4" s="14">
@@ -3440,7 +3453,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D5" s="13">
@@ -3461,7 +3474,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="13">
@@ -3482,7 +3495,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="14">
@@ -3503,7 +3516,7 @@
         <f>TEXT(A8,"mmmm")</f>
         <v>October</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="13">
@@ -3524,7 +3537,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="13">
@@ -3545,7 +3558,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="13">
@@ -3566,7 +3579,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="43" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="13">
@@ -3587,7 +3600,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="14">
@@ -3611,7 +3624,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="13">
@@ -3632,7 +3645,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D14" s="14">
@@ -3653,7 +3666,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D15" s="13">
@@ -3674,7 +3687,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="43" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="13">
@@ -3695,7 +3708,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="43" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="13">
@@ -3716,7 +3729,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="13">
@@ -3737,7 +3750,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D19" s="13">
@@ -3758,7 +3771,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="43" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="13">
@@ -3779,7 +3792,7 @@
         <f t="shared" si="0"/>
         <v>October</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D21" s="13">
@@ -3800,7 +3813,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="43" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="14">
@@ -3821,7 +3834,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="13">
@@ -3842,7 +3855,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="14">
@@ -3863,7 +3876,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D25" s="13">
@@ -3884,7 +3897,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D26" s="13">
@@ -3905,7 +3918,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D27" s="14">
@@ -3926,7 +3939,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D28" s="13">
@@ -3947,7 +3960,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="13">
@@ -3968,7 +3981,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D30" s="13">
@@ -3989,7 +4002,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="13">
@@ -4010,7 +4023,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="13">
@@ -4031,7 +4044,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="43" t="s">
         <v>9</v>
       </c>
       <c r="D33" s="13">
@@ -4052,7 +4065,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="13">
@@ -4073,7 +4086,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D35" s="13">
@@ -4094,7 +4107,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D36" s="14">
@@ -4115,7 +4128,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D37" s="13">
@@ -4136,7 +4149,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="13">
@@ -4157,7 +4170,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="13">
@@ -4178,7 +4191,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="43" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="14">
@@ -4199,7 +4212,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="13">
@@ -4220,7 +4233,7 @@
         <f t="shared" si="0"/>
         <v>November</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="43" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="13">
@@ -4241,7 +4254,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="43" t="s">
         <v>4</v>
       </c>
       <c r="D43" s="14">
@@ -4262,7 +4275,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D44" s="13">
@@ -4283,7 +4296,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="43" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="13">
@@ -4304,7 +4317,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="43" t="s">
         <v>12</v>
       </c>
       <c r="D46" s="13">
@@ -4325,7 +4338,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="43" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="13">
@@ -4346,7 +4359,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="13">
@@ -4367,7 +4380,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="43" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="13">
@@ -4388,7 +4401,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="43" t="s">
         <v>6</v>
       </c>
       <c r="D50" s="13">
@@ -4409,7 +4422,7 @@
         <f t="shared" si="0"/>
         <v>December</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="43" t="s">
         <v>5</v>
       </c>
       <c r="D51" s="13">
@@ -4435,7 +4448,7 @@
       <c r="B53" s="1"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations disablePrompts="1" count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E51" xr:uid="{757D7536-5ADE-4F67-88EB-D7AF0E8BAC0E}">
       <formula1>"Essential, Non-essential"</formula1>
     </dataValidation>
@@ -4512,7 +4525,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="23.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.1796875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="33.54296875" style="16" customWidth="1"/>
     <col min="5" max="5" width="17.54296875" customWidth="1"/>
     <col min="6" max="6" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19.7265625" bestFit="1" customWidth="1"/>
@@ -4582,7 +4595,7 @@
       <c r="H10" s="19"/>
       <c r="I10" s="19"/>
     </row>
-    <row r="12" spans="3:14" ht="27" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:14" x14ac:dyDescent="0.35">
       <c r="C12" s="23" t="s">
         <v>14</v>
       </c>
@@ -4700,110 +4713,146 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
     </row>
-    <row r="28" spans="3:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="28" spans="3:9" x14ac:dyDescent="0.35">
       <c r="C28" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D28" s="28" t="s">
+      <c r="D28" s="39" t="s">
         <v>39</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C29" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C29,Expense!D:D)</f>
-        <v>7775</v>
+      <c r="D29" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C39,Expense!D:D))</f>
+        <v>12000</v>
+      </c>
+      <c r="E29" s="41">
+        <v>1411.26</v>
       </c>
     </row>
     <row r="30" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C30" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C30,Expense!D:D)</f>
-        <v>7464</v>
+      <c r="D30" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C38,Expense!D:D))</f>
+        <v>1510.9099999999999</v>
+      </c>
+      <c r="E30" s="41">
+        <v>1510.9099999999999</v>
       </c>
     </row>
     <row r="31" spans="3:9" ht="30" x14ac:dyDescent="0.35">
       <c r="C31" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C31,Expense!D:D)</f>
-        <v>10194.1</v>
+      <c r="D31" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C37,Expense!D:D))</f>
+        <v>1411.26</v>
+      </c>
+      <c r="E31" s="41">
+        <v>1857</v>
       </c>
     </row>
     <row r="32" spans="3:9" ht="15" x14ac:dyDescent="0.35">
       <c r="C32" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C32,Expense!D:D)</f>
-        <v>3217</v>
+      <c r="D32" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C36,Expense!D:D))</f>
+        <v>2586</v>
+      </c>
+      <c r="E32" s="41">
+        <v>2586</v>
       </c>
     </row>
     <row r="33" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C33" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C33,Expense!D:D)</f>
-        <v>3342</v>
+      <c r="D33" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C35,Expense!D:D))</f>
+        <v>1857</v>
+      </c>
+      <c r="E33" s="41">
+        <v>3217</v>
       </c>
     </row>
     <row r="34" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C34" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C34,Expense!D:D)</f>
+      <c r="D34" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C34,Expense!D:D))</f>
         <v>5688</v>
+      </c>
+      <c r="E34" s="41">
+        <v>3342</v>
       </c>
     </row>
     <row r="35" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C35" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="D35" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C35,Expense!D:D)</f>
-        <v>1857</v>
+      <c r="D35" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C33,Expense!D:D))</f>
+        <v>3342</v>
+      </c>
+      <c r="E35" s="41">
+        <v>5688</v>
       </c>
     </row>
     <row r="36" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C36" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C36,Expense!D:D)</f>
-        <v>2586</v>
+      <c r="D36" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C32,Expense!D:D))</f>
+        <v>3217</v>
+      </c>
+      <c r="E36" s="41">
+        <v>7464</v>
       </c>
     </row>
     <row r="37" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C37" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C37,Expense!D:D)</f>
-        <v>1411.26</v>
+      <c r="D37" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C31,Expense!D:D))</f>
+        <v>10194.1</v>
+      </c>
+      <c r="E37" s="41">
+        <v>7775</v>
       </c>
     </row>
     <row r="38" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C38" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="D38" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C38,Expense!D:D)</f>
-        <v>1510.9099999999999</v>
+      <c r="D38" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C30,Expense!D:D))</f>
+        <v>7464</v>
+      </c>
+      <c r="E38" s="41">
+        <v>10194.1</v>
       </c>
     </row>
     <row r="39" spans="3:24" ht="15" x14ac:dyDescent="0.35">
       <c r="C39" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D39" s="27">
-        <f>SUMIF(Expense!C:C,Sheet1!C39,Expense!D:D)</f>
+      <c r="D39" s="40">
+        <f>VALUE(SUMIF(Expense!C:C,Sheet1!C29,Expense!D:D))</f>
+        <v>7775</v>
+      </c>
+      <c r="E39" s="41">
         <v>12000</v>
       </c>
     </row>
@@ -4833,7 +4882,7 @@
       <c r="W42" s="19"/>
       <c r="X42" s="19"/>
     </row>
-    <row r="44" spans="3:24" ht="27" x14ac:dyDescent="0.35">
+    <row r="44" spans="3:24" x14ac:dyDescent="0.35">
       <c r="C44" s="23" t="s">
         <v>14</v>
       </c>
@@ -5088,7 +5137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="81" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C81" s="6">
         <v>44470</v>
       </c>
@@ -5102,7 +5151,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="82" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C82" s="6">
         <v>44470</v>
       </c>
@@ -5116,7 +5165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="83" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C83" s="6">
         <v>44473</v>
       </c>
@@ -5172,7 +5221,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="87" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C87" s="6">
         <v>44484</v>
       </c>
@@ -5186,7 +5235,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="88" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C88" s="6">
         <v>44485</v>
       </c>
@@ -5200,7 +5249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="89" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C89" s="6">
         <v>44487</v>
       </c>
@@ -5242,7 +5291,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="92" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C92" s="6">
         <v>44491</v>
       </c>
@@ -5298,7 +5347,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="96" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C96" s="6">
         <v>44496</v>
       </c>
@@ -5312,7 +5361,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="97" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C97" s="4">
         <v>44497</v>
       </c>
@@ -5340,7 +5389,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="99" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C99" s="4">
         <v>44499</v>
       </c>
@@ -5354,7 +5403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="100" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C100" s="6">
         <v>44501</v>
       </c>
@@ -5396,7 +5445,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="103" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C103" s="4">
         <v>44505</v>
       </c>
@@ -5424,7 +5473,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="105" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C105" s="6">
         <v>44509</v>
       </c>
@@ -5438,7 +5487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="106" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C106" s="6">
         <v>44512</v>
       </c>
@@ -5452,7 +5501,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="107" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C107" s="4">
         <v>44515</v>
       </c>
@@ -5494,7 +5543,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="110" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C110" s="4">
         <v>44517</v>
       </c>
@@ -5522,7 +5571,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="112" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C112" s="4">
         <v>44518</v>
       </c>
@@ -5536,7 +5585,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="113" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C113" s="4">
         <v>44519</v>
       </c>
@@ -5550,7 +5599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="114" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C114" s="4">
         <v>44522</v>
       </c>
@@ -5592,7 +5641,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="117" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C117" s="4">
         <v>44526</v>
       </c>
@@ -5606,7 +5655,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="118" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C118" s="4">
         <v>44526</v>
       </c>
@@ -5634,7 +5683,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="120" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C120" s="4">
         <v>44530</v>
       </c>
@@ -5648,7 +5697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="121" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C121" s="4">
         <v>44531</v>
       </c>
@@ -5662,7 +5711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="122" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C122" s="6">
         <v>44534</v>
       </c>
@@ -5718,7 +5767,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="126" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C126" s="4">
         <v>44547</v>
       </c>
@@ -5760,7 +5809,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="129" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="129" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C129" s="4">
         <v>44553</v>
       </c>
@@ -5828,7 +5877,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="136" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C136" s="6">
         <v>44470</v>
       </c>
@@ -5842,7 +5891,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="137" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C137" s="6">
         <v>44470</v>
       </c>
@@ -5856,7 +5905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="138" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C138" s="6">
         <v>44473</v>
       </c>
@@ -5912,7 +5961,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="142" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C142" s="6">
         <v>44484</v>
       </c>
@@ -5926,7 +5975,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="143" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="143" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C143" s="6">
         <v>44485</v>
       </c>
@@ -5940,7 +5989,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="144" spans="3:20" ht="27" x14ac:dyDescent="0.35">
+    <row r="144" spans="3:20" x14ac:dyDescent="0.35">
       <c r="C144" s="6">
         <v>44487</v>
       </c>
@@ -5982,7 +6031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="147" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C147" s="6">
         <v>44491</v>
       </c>
@@ -6038,7 +6087,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="151" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="151" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C151" s="6">
         <v>44496</v>
       </c>
@@ -6052,7 +6101,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="152" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C152" s="4">
         <v>44497</v>
       </c>
@@ -6080,7 +6129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="154" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="154" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C154" s="4">
         <v>44499</v>
       </c>
@@ -6094,7 +6143,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="155" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="155" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C155" s="6">
         <v>44501</v>
       </c>
@@ -6136,7 +6185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="158" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C158" s="4">
         <v>44505</v>
       </c>
@@ -6164,7 +6213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="160" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C160" s="6">
         <v>44509</v>
       </c>
@@ -6178,7 +6227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="161" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="161" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C161" s="6">
         <v>44512</v>
       </c>
@@ -6192,7 +6241,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="162" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C162" s="4">
         <v>44515</v>
       </c>
@@ -6234,7 +6283,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="165" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C165" s="4">
         <v>44517</v>
       </c>
@@ -6262,7 +6311,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="167" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C167" s="4">
         <v>44518</v>
       </c>
@@ -6276,7 +6325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="168" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C168" s="4">
         <v>44519</v>
       </c>
@@ -6290,7 +6339,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="169" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="169" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C169" s="4">
         <v>44522</v>
       </c>
@@ -6332,7 +6381,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="172" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C172" s="4">
         <v>44526</v>
       </c>
@@ -6346,7 +6395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="173" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C173" s="4">
         <v>44526</v>
       </c>
@@ -6374,7 +6423,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="175" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C175" s="4">
         <v>44530</v>
       </c>
@@ -6388,7 +6437,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="3:6" ht="27" x14ac:dyDescent="0.35">
+    <row r="176" spans="3:6" x14ac:dyDescent="0.35">
       <c r="C176" s="4">
         <v>44531</v>
       </c>
@@ -6402,7 +6451,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" spans="3:8" ht="27" x14ac:dyDescent="0.35">
+    <row r="177" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C177" s="6">
         <v>44534</v>
       </c>
@@ -6458,7 +6507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="3:8" ht="27" x14ac:dyDescent="0.35">
+    <row r="181" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C181" s="4">
         <v>44547</v>
       </c>
@@ -6500,7 +6549,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="3:8" ht="27" x14ac:dyDescent="0.35">
+    <row r="184" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C184" s="4">
         <v>44553</v>
       </c>
@@ -6574,6 +6623,9 @@
       <c r="E195" s="38"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C29:E39">
+    <sortCondition ref="E29:E39"/>
+  </sortState>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F80:F129" xr:uid="{F412C911-2663-46E0-AF2D-A7A4EB308882}">
       <formula1>"Essential, Non-essential"</formula1>
